--- a/demo-output/hq-daily-4sheet-demo.xlsx
+++ b/demo-output/hq-daily-4sheet-demo.xlsx
@@ -3,10 +3,10 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales List" sheetId="1" r:id="rId1"/>
-    <x:sheet name="Today Sales" sheetId="2" r:id="R7a5f49c889274901"/>
-    <x:sheet name="Fish Sales" sheetId="3" r:id="R673ce3e706f64603"/>
-    <x:sheet name="Sales Detail" sheetId="4" r:id="R83f6fb2aa54549d6"/>
-    <x:sheet name="Credit" sheetId="5" r:id="Ref61d70ee95148b8"/>
+    <x:sheet name="Today Sales" sheetId="2" r:id="Re81885e9ccdf4677"/>
+    <x:sheet name="Fish Sales" sheetId="3" r:id="R1c3c517911e8489f"/>
+    <x:sheet name="Sales Detail" sheetId="4" r:id="Re3f4f2afb96d4096"/>
+    <x:sheet name="Credit" sheetId="5" r:id="Refeda3c8d2374c14"/>
   </x:sheets>
   <x:calcPr fullCalcOnLoad="1"/>
 </x:workbook>
@@ -700,33 +700,45 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>Cash (2)</x:v>
-      </x:c>
-      <x:c r="C15" s="6">
+        <x:v>Cash</x:v>
+      </x:c>
+      <x:c r="C15" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D15" s="6">
         <x:v>574.75</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>QR (2)</x:v>
-      </x:c>
-      <x:c r="C16" s="6">
+        <x:v>QR</x:v>
+      </x:c>
+      <x:c r="C16" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D16" s="6">
         <x:v>97.2</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>Credit (2)</x:v>
-      </x:c>
-      <x:c r="C17" s="6">
+        <x:v>Credit</x:v>
+      </x:c>
+      <x:c r="C17" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D17" s="6">
         <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>Bank (1)</x:v>
-      </x:c>
-      <x:c r="C18" s="6">
+        <x:v>Bank</x:v>
+      </x:c>
+      <x:c r="C18" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D18" s="6">
         <x:v>142</x:v>
       </x:c>
     </x:row>
@@ -1562,12 +1574,73 @@
         <x:v>614.7</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="12" t="str">
+        <x:v>BY CREDITOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="3" t="str">
+        <x:v>Name</x:v>
+      </x:c>
+      <x:c r="C20" s="4" t="str">
+        <x:v>Invoices</x:v>
+      </x:c>
+      <x:c r="D20" s="4" t="str">
+        <x:v>Amount (RM)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Pak Abu</x:v>
+      </x:c>
+      <x:c r="C21" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D21" s="6">
+        <x:v>251.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Restoran Selera</x:v>
+      </x:c>
+      <x:c r="C22" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D22" s="6">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Kak Ros</x:v>
+      </x:c>
+      <x:c r="C23" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D23" s="6">
+        <x:v>123.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="7" t="str">
+        <x:v>TOTAL</x:v>
+      </x:c>
+      <x:c r="B24" s="8"/>
+      <x:c r="C24" s="8"/>
+      <x:c r="D24" s="9">
+        <x:f>SUM(D21:D23)</x:f>
+        <x:v>614.7</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:mergeCells count="4">
+  <x:mergeCells count="5">
     <x:mergeCell ref="A1:D1"/>
     <x:mergeCell ref="A2:D2"/>
     <x:mergeCell ref="A4:D4"/>
     <x:mergeCell ref="A10:D10"/>
+    <x:mergeCell ref="A19:D19"/>
   </x:mergeCells>
 </x:worksheet>
 </file>
--- a/demo-output/hq-daily-4sheet-demo.xlsx
+++ b/demo-output/hq-daily-4sheet-demo.xlsx
@@ -3,10 +3,10 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales List" sheetId="1" r:id="rId1"/>
-    <x:sheet name="Today Sales" sheetId="2" r:id="Re81885e9ccdf4677"/>
-    <x:sheet name="Fish Sales" sheetId="3" r:id="R1c3c517911e8489f"/>
-    <x:sheet name="Sales Detail" sheetId="4" r:id="Re3f4f2afb96d4096"/>
-    <x:sheet name="Credit" sheetId="5" r:id="Refeda3c8d2374c14"/>
+    <x:sheet name="Today Sales" sheetId="2" r:id="Rd427627925f94f6e"/>
+    <x:sheet name="Fish Sales" sheetId="3" r:id="R81bd878755cc418f"/>
+    <x:sheet name="Sales Detail" sheetId="4" r:id="R9ea4b91ea79a4ffe"/>
+    <x:sheet name="Credit" sheetId="5" r:id="Rb8f5b06568664b83"/>
   </x:sheets>
   <x:calcPr fullCalcOnLoad="1"/>
 </x:workbook>
@@ -39,6 +39,11 @@
       <x:name val="Calibri"/>
     </x:font>
     <x:font>
+      <x:strike/>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
       <x:b/>
       <x:sz val="9"/>
       <x:color rgb="FF666666"/>
@@ -46,11 +51,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:strike/>
-      <x:sz val="11"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
       <x:strike/>
       <x:sz val="11"/>
       <x:name val="Calibri"/>
@@ -184,7 +184,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -201,19 +201,22 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyFont="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1"/>
     <x:xf numFmtId="4" fontId="3" fillId="0" borderId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="1"/>
+    <x:xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1"/>
+    <x:xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <x:alignment horizontal="right"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyFont="1" applyFill="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyBorder="1"/>
@@ -225,19 +228,19 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyFont="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyBorder="1"/>
     <x:xf numFmtId="4" fontId="3" fillId="0" borderId="11" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right"/>
     </x:xf>
-    <x:xf numFmtId="4" fontId="6" fillId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="4" fontId="6" fillId="0" borderId="8" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="4" fontId="5" fillId="0" borderId="11" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="4" fontId="4" fillId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="4" fontId="4" fillId="0" borderId="8" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="4" fontId="6" fillId="0" borderId="11" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyFont="1" applyFill="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyFont="1" applyFill="1"/>
   </x:cellXfs>
@@ -362,12 +365,13 @@
     <x:tabColor rgb="FF217346"/>
   </x:sheetPr>
   <x:cols>
-    <x:col min="1" max="1" width="24" customWidth="1"/>
-    <x:col min="2" max="2" width="12" customWidth="1"/>
-    <x:col min="3" max="3" width="10" customWidth="1"/>
-    <x:col min="4" max="4" width="12" customWidth="1"/>
-    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="1" max="1" width="6" customWidth="1"/>
+    <x:col min="2" max="2" width="24" customWidth="1"/>
+    <x:col min="3" max="3" width="12" customWidth="1"/>
+    <x:col min="4" max="4" width="10" customWidth="1"/>
+    <x:col min="5" max="5" width="12" customWidth="1"/>
     <x:col min="6" max="6" width="14" customWidth="1"/>
+    <x:col min="7" max="7" width="14" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -382,140 +386,164 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="3" t="str">
+        <x:v>#</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="C4" s="3" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="D4" s="3" t="str">
         <x:v>Inv No</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="E4" s="3" t="str">
         <x:v>Pay Type</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="str">
+      <x:c r="F4" s="4" t="str">
         <x:v>Cash (RM)</x:v>
       </x:c>
-      <x:c r="F4" s="4" t="str">
+      <x:c r="G4" s="4" t="str">
         <x:v>Credit (RM)</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
+      <x:c r="A5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
         <x:v/>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="C5" s="5" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="C5">
+      <x:c r="D5">
         <x:v>1001</x:v>
       </x:c>
-      <x:c r="D5" t="str">
+      <x:c r="E5" t="str">
         <x:v>Cash</x:v>
       </x:c>
-      <x:c r="E5" s="6">
+      <x:c r="F5" s="6">
         <x:v>374.75</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
+      <x:c r="A6">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
         <x:v/>
       </x:c>
-      <x:c r="B6" s="5" t="str">
+      <x:c r="C6" s="5" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="C6">
+      <x:c r="D6">
         <x:v>1002</x:v>
       </x:c>
-      <x:c r="D6" t="str">
+      <x:c r="E6" t="str">
         <x:v>QR</x:v>
       </x:c>
-      <x:c r="E6" s="6">
+      <x:c r="F6" s="6">
         <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
+      <x:c r="A7">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
         <x:v>Pak Abu</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="str">
+      <x:c r="C7" s="5" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="C7">
+      <x:c r="D7">
         <x:v>1003</x:v>
       </x:c>
-      <x:c r="D7" t="str">
+      <x:c r="E7" t="str">
         <x:v>Credit</x:v>
       </x:c>
-      <x:c r="F7" s="6">
+      <x:c r="G7" s="6">
         <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
+      <x:c r="A8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
         <x:v/>
       </x:c>
-      <x:c r="B8" s="5" t="str">
+      <x:c r="C8" s="5" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="C8">
+      <x:c r="D8">
         <x:v>1004</x:v>
       </x:c>
-      <x:c r="D8" t="str">
+      <x:c r="E8" t="str">
         <x:v>Bank</x:v>
       </x:c>
-      <x:c r="E8" s="6">
+      <x:c r="F8" s="6">
         <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
+      <x:c r="A9">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
         <x:v/>
       </x:c>
-      <x:c r="B9" s="5" t="str">
+      <x:c r="C9" s="5" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="C9">
+      <x:c r="D9">
         <x:v>1005</x:v>
       </x:c>
-      <x:c r="D9" t="str">
+      <x:c r="E9" t="str">
         <x:v>Cash</x:v>
       </x:c>
-      <x:c r="E9" s="6">
+      <x:c r="F9" s="6">
         <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
+      <x:c r="A10">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
         <x:v>Kak Ros</x:v>
       </x:c>
-      <x:c r="B10" s="5" t="str">
+      <x:c r="C10" s="5" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="C10">
+      <x:c r="D10">
         <x:v>1006</x:v>
       </x:c>
-      <x:c r="D10" t="str">
+      <x:c r="E10" t="str">
         <x:v>Credit</x:v>
       </x:c>
-      <x:c r="F10" s="6">
+      <x:c r="G10" s="6">
         <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
+      <x:c r="A11">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
         <x:v/>
       </x:c>
-      <x:c r="B11" s="5" t="str">
+      <x:c r="C11" s="5" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="C11">
+      <x:c r="D11">
         <x:v>1008</x:v>
       </x:c>
-      <x:c r="D11" t="str">
+      <x:c r="E11" t="str">
         <x:v>QR</x:v>
       </x:c>
-      <x:c r="E11" s="6">
+      <x:c r="F11" s="6">
         <x:v>34.2</x:v>
       </x:c>
     </x:row>
@@ -526,24 +554,48 @@
       <x:c r="B12" s="8"/>
       <x:c r="C12" s="8"/>
       <x:c r="D12" s="8"/>
-      <x:c r="E12" s="9">
-        <x:f>SUM(E5:E11)</x:f>
-        <x:v>813.95</x:v>
-      </x:c>
+      <x:c r="E12" s="8"/>
       <x:c r="F12" s="9">
         <x:f>SUM(F5:F11)</x:f>
+        <x:v>813.95</x:v>
+      </x:c>
+      <x:c r="G12" s="9">
+        <x:f>SUM(G5:G11)</x:f>
         <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="10" t="str">
+        <x:v>CANCELLED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="B15" s="11" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="C15" s="12" t="str">
+        <x:v>2026-08-10</x:v>
+      </x:c>
+      <x:c r="D15" s="11">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str">
+        <x:v>Cash</x:v>
+      </x:c>
+      <x:c r="F15" s="13">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="14" t="str">
         <x:v>7 sale(s), 1 voided</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="2">
-    <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A2:F2"/>
+  <x:mergeCells count="3">
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A14:G14"/>
   </x:mergeCells>
 </x:worksheet>
 </file>
@@ -591,7 +643,7 @@
       <x:c r="B5" s="6">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="str">
+      <x:c r="C5" s="15" t="str">
         <x:v>27.35 kg</x:v>
       </x:c>
       <x:c r="D5" s="6">
@@ -605,7 +657,7 @@
       <x:c r="B6" s="6">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="str">
+      <x:c r="C6" s="15" t="str">
         <x:v>3.5 kg</x:v>
       </x:c>
       <x:c r="D6" s="6">
@@ -619,7 +671,7 @@
       <x:c r="B7" s="6">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="str">
+      <x:c r="C7" s="15" t="str">
         <x:v>4 kg</x:v>
       </x:c>
       <x:c r="D7" s="6">
@@ -633,7 +685,7 @@
       <x:c r="B8" s="6">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="str">
+      <x:c r="C8" s="15" t="str">
         <x:v>5 ekor</x:v>
       </x:c>
       <x:c r="D8" s="6">
@@ -647,7 +699,7 @@
       <x:c r="B9" s="6">
         <x:v>6.8</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="str">
+      <x:c r="C9" s="15" t="str">
         <x:v>4 bottle</x:v>
       </x:c>
       <x:c r="D9" s="6">
@@ -661,7 +713,7 @@
       <x:c r="B10" s="6">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="str">
+      <x:c r="C10" s="15" t="str">
         <x:v>3 kg</x:v>
       </x:c>
       <x:c r="D10" s="6">
@@ -675,7 +727,7 @@
       <x:c r="B11" s="6">
         <x:v>3.5</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="str">
+      <x:c r="C11" s="15" t="str">
         <x:v>4 bag</x:v>
       </x:c>
       <x:c r="D11" s="6">
@@ -694,7 +746,7 @@
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="12" t="str">
+      <x:c r="A14" s="10" t="str">
         <x:v>BY PAYMENT</x:v>
       </x:c>
     </x:row>
@@ -702,7 +754,7 @@
       <x:c r="A15" t="str">
         <x:v>Cash</x:v>
       </x:c>
-      <x:c r="C15" s="11">
+      <x:c r="C15" s="15">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D15" s="6">
@@ -713,7 +765,7 @@
       <x:c r="A16" t="str">
         <x:v>QR</x:v>
       </x:c>
-      <x:c r="C16" s="11">
+      <x:c r="C16" s="15">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D16" s="6">
@@ -724,7 +776,7 @@
       <x:c r="A17" t="str">
         <x:v>Credit</x:v>
       </x:c>
-      <x:c r="C17" s="11">
+      <x:c r="C17" s="15">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D17" s="6">
@@ -735,7 +787,7 @@
       <x:c r="A18" t="str">
         <x:v>Bank</x:v>
       </x:c>
-      <x:c r="C18" s="11">
+      <x:c r="C18" s="15">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="6">
@@ -743,7 +795,7 @@
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="10" t="str">
+      <x:c r="A19" s="14" t="str">
         <x:v>7 sale(s), 1 voided</x:v>
       </x:c>
     </x:row>
@@ -762,11 +814,12 @@
     <x:tabColor rgb="FF2E75B6"/>
   </x:sheetPr>
   <x:cols>
-    <x:col min="1" max="1" width="10" customWidth="1"/>
-    <x:col min="2" max="2" width="12" customWidth="1"/>
-    <x:col min="3" max="3" width="14" customWidth="1"/>
+    <x:col min="1" max="1" width="6" customWidth="1"/>
+    <x:col min="2" max="2" width="10" customWidth="1"/>
+    <x:col min="3" max="3" width="12" customWidth="1"/>
     <x:col min="4" max="4" width="14" customWidth="1"/>
-    <x:col min="5" max="5" width="16" customWidth="1"/>
+    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="6" max="6" width="16" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -781,74 +834,89 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="3" t="str">
+        <x:v>#</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="str">
         <x:v>Inv No</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="C4" s="3" t="str">
         <x:v>Pay Type</x:v>
       </x:c>
-      <x:c r="C4" s="4" t="str">
+      <x:c r="D4" s="4" t="str">
         <x:v>Cash (RM)</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="str">
+      <x:c r="E4" s="4" t="str">
         <x:v>Credit (RM)</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="str">
+      <x:c r="F4" s="4" t="str">
         <x:v>Fish Qty (Ekor)</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5">
         <x:v>1001</x:v>
       </x:c>
-      <x:c r="B5" t="str">
+      <x:c r="C5" t="str">
         <x:v>Cash</x:v>
       </x:c>
-      <x:c r="C5" s="6">
+      <x:c r="D5" s="6">
         <x:v>374.75</x:v>
       </x:c>
-      <x:c r="E5">
+      <x:c r="F5">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6">
         <x:v>1003</x:v>
       </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="C6" t="str">
         <x:v>Credit</x:v>
       </x:c>
-      <x:c r="D6" s="6">
+      <x:c r="E6" s="6">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="E6">
+      <x:c r="F6">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7">
         <x:v>1005</x:v>
       </x:c>
-      <x:c r="B7" t="str">
+      <x:c r="C7" t="str">
         <x:v>Cash</x:v>
       </x:c>
-      <x:c r="C7" s="6">
+      <x:c r="D7" s="6">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="E7">
+      <x:c r="F7">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8">
         <x:v>1006</x:v>
       </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="C8" t="str">
         <x:v>Credit</x:v>
       </x:c>
-      <x:c r="D8" s="6">
+      <x:c r="E8" s="6">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E8">
+      <x:c r="F8">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -857,23 +925,24 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="B9" s="8"/>
-      <x:c r="C9" s="9">
-        <x:f>SUM(C5:C8)</x:f>
-        <x:v>574.75</x:v>
-      </x:c>
+      <x:c r="C9" s="8"/>
       <x:c r="D9" s="9">
         <x:f>SUM(D5:D8)</x:f>
+        <x:v>574.75</x:v>
+      </x:c>
+      <x:c r="E9" s="9">
+        <x:f>SUM(E5:E8)</x:f>
         <x:v>234</x:v>
       </x:c>
-      <x:c r="E9" s="7">
-        <x:f>SUM(E5:E8)</x:f>
+      <x:c r="F9" s="7">
+        <x:f>SUM(F5:F8)</x:f>
         <x:v>38</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="2">
-    <x:mergeCell ref="A1:E1"/>
-    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
 </x:worksheet>
 </file>
@@ -901,488 +970,488 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="13" t="str">
+      <x:c r="A4" s="16" t="str">
         <x:v>Inv #1001</x:v>
       </x:c>
-      <x:c r="B4" s="14" t="str">
+      <x:c r="B4" s="17" t="str">
         <x:v>08:15</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="str">
+      <x:c r="C4" s="17" t="str">
         <x:v>Cash</x:v>
       </x:c>
-      <x:c r="D4" s="15"/>
+      <x:c r="D4" s="18"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A5" s="19" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B5" s="17" t="str">
+      <x:c r="B5" s="20" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="C5" s="17" t="str">
+      <x:c r="C5" s="20" t="str">
         <x:v>Price (RM)</x:v>
       </x:c>
-      <x:c r="D5" s="18" t="str">
+      <x:c r="D5" s="21" t="str">
         <x:v>Amount (RM)</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="19" t="str">
+      <x:c r="A6" s="22" t="str">
         <x:v>Ikan Tilapia (18 ekor)</x:v>
       </x:c>
-      <x:c r="B6" s="20" t="str">
+      <x:c r="B6" s="23" t="str">
         <x:v>12.75 kg</x:v>
       </x:c>
-      <x:c r="C6" s="21">
+      <x:c r="C6" s="24">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D6" s="22">
+      <x:c r="D6" s="25">
         <x:v>318.75</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="19" t="str">
+      <x:c r="A7" s="22" t="str">
         <x:v>Sotong</x:v>
       </x:c>
-      <x:c r="B7" s="20" t="str">
+      <x:c r="B7" s="23" t="str">
         <x:v>2 kg</x:v>
       </x:c>
-      <x:c r="C7" s="21">
+      <x:c r="C7" s="24">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D7" s="22">
+      <x:c r="D7" s="25">
         <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="23" t="str">
+      <x:c r="A8" s="26" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B8" s="24"/>
-      <x:c r="C8" s="24"/>
-      <x:c r="D8" s="25">
+      <x:c r="B8" s="27"/>
+      <x:c r="C8" s="27"/>
+      <x:c r="D8" s="28">
         <x:v>374.75</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="13" t="str">
+      <x:c r="A10" s="16" t="str">
         <x:v>Inv #1002</x:v>
       </x:c>
-      <x:c r="B10" s="14" t="str">
+      <x:c r="B10" s="17" t="str">
         <x:v>09:05</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="str">
+      <x:c r="C10" s="17" t="str">
         <x:v>QR</x:v>
       </x:c>
-      <x:c r="D10" s="15"/>
+      <x:c r="D10" s="18"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="16" t="str">
+      <x:c r="A11" s="19" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="str">
+      <x:c r="B11" s="20" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str">
+      <x:c r="C11" s="20" t="str">
         <x:v>Price (RM)</x:v>
       </x:c>
-      <x:c r="D11" s="18" t="str">
+      <x:c r="D11" s="21" t="str">
         <x:v>Amount (RM)</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="19" t="str">
+      <x:c r="A12" s="22" t="str">
         <x:v>Sotong</x:v>
       </x:c>
-      <x:c r="B12" s="20" t="str">
+      <x:c r="B12" s="23" t="str">
         <x:v>2 kg</x:v>
       </x:c>
-      <x:c r="C12" s="21">
+      <x:c r="C12" s="24">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D12" s="22">
+      <x:c r="D12" s="25">
         <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="19" t="str">
+      <x:c r="A13" s="22" t="str">
         <x:v>Ais Tube</x:v>
       </x:c>
-      <x:c r="B13" s="20" t="str">
+      <x:c r="B13" s="23" t="str">
         <x:v>2 bag</x:v>
       </x:c>
-      <x:c r="C13" s="21">
+      <x:c r="C13" s="24">
         <x:v>3.5</x:v>
       </x:c>
-      <x:c r="D13" s="22">
+      <x:c r="D13" s="25">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="23" t="str">
+      <x:c r="A14" s="26" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B14" s="24"/>
-      <x:c r="C14" s="24"/>
-      <x:c r="D14" s="25">
+      <x:c r="B14" s="27"/>
+      <x:c r="C14" s="27"/>
+      <x:c r="D14" s="28">
         <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="13" t="str">
+      <x:c r="A16" s="16" t="str">
         <x:v>Inv #1003 — Pak Abu</x:v>
       </x:c>
-      <x:c r="B16" s="14" t="str">
+      <x:c r="B16" s="17" t="str">
         <x:v>09:40</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="str">
+      <x:c r="C16" s="17" t="str">
         <x:v>Credit</x:v>
       </x:c>
-      <x:c r="D16" s="15"/>
+      <x:c r="D16" s="18"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="16" t="str">
+      <x:c r="A17" s="19" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B17" s="17" t="str">
+      <x:c r="B17" s="20" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="str">
+      <x:c r="C17" s="20" t="str">
         <x:v>Price (RM)</x:v>
       </x:c>
-      <x:c r="D17" s="18" t="str">
+      <x:c r="D17" s="21" t="str">
         <x:v>Amount (RM)</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="19" t="str">
+      <x:c r="A18" s="22" t="str">
         <x:v>Ikan Tilapia (6 ekor)</x:v>
       </x:c>
-      <x:c r="B18" s="20" t="str">
+      <x:c r="B18" s="23" t="str">
         <x:v>4.2 kg</x:v>
       </x:c>
-      <x:c r="C18" s="21">
+      <x:c r="C18" s="24">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D18" s="22">
+      <x:c r="D18" s="25">
         <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="19" t="str">
+      <x:c r="A19" s="22" t="str">
         <x:v>Ayam</x:v>
       </x:c>
-      <x:c r="B19" s="20" t="str">
+      <x:c r="B19" s="23" t="str">
         <x:v>5 ekor</x:v>
       </x:c>
-      <x:c r="C19" s="21">
+      <x:c r="C19" s="24">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D19" s="22">
+      <x:c r="D19" s="25">
         <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="23" t="str">
+      <x:c r="A20" s="26" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B20" s="24"/>
-      <x:c r="C20" s="24"/>
-      <x:c r="D20" s="25">
+      <x:c r="B20" s="27"/>
+      <x:c r="C20" s="27"/>
+      <x:c r="D20" s="28">
         <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="13" t="str">
+      <x:c r="A22" s="16" t="str">
         <x:v>Inv #1004</x:v>
       </x:c>
-      <x:c r="B22" s="14" t="str">
+      <x:c r="B22" s="17" t="str">
         <x:v>11:05</x:v>
       </x:c>
-      <x:c r="C22" s="14" t="str">
+      <x:c r="C22" s="17" t="str">
         <x:v>Bank</x:v>
       </x:c>
-      <x:c r="D22" s="15"/>
+      <x:c r="D22" s="18"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="16" t="str">
+      <x:c r="A23" s="19" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B23" s="17" t="str">
+      <x:c r="B23" s="20" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="C23" s="17" t="str">
+      <x:c r="C23" s="20" t="str">
         <x:v>Price (RM)</x:v>
       </x:c>
-      <x:c r="D23" s="18" t="str">
+      <x:c r="D23" s="21" t="str">
         <x:v>Amount (RM)</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="19" t="str">
+      <x:c r="A24" s="22" t="str">
         <x:v>Udang</x:v>
       </x:c>
-      <x:c r="B24" s="20" t="str">
+      <x:c r="B24" s="23" t="str">
         <x:v>3.5 kg</x:v>
       </x:c>
-      <x:c r="C24" s="21">
+      <x:c r="C24" s="24">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D24" s="22">
+      <x:c r="D24" s="25">
         <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="19" t="str">
+      <x:c r="A25" s="22" t="str">
         <x:v>Sayur Campur</x:v>
       </x:c>
-      <x:c r="B25" s="20" t="str">
+      <x:c r="B25" s="23" t="str">
         <x:v>1.5 kg</x:v>
       </x:c>
-      <x:c r="C25" s="21">
+      <x:c r="C25" s="24">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D25" s="22">
+      <x:c r="D25" s="25">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="23" t="str">
+      <x:c r="A26" s="26" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B26" s="24"/>
-      <x:c r="C26" s="24"/>
-      <x:c r="D26" s="25">
+      <x:c r="B26" s="27"/>
+      <x:c r="C26" s="27"/>
+      <x:c r="D26" s="28">
         <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="13" t="str">
+      <x:c r="A28" s="16" t="str">
         <x:v>Inv #1005</x:v>
       </x:c>
-      <x:c r="B28" s="14" t="str">
+      <x:c r="B28" s="17" t="str">
         <x:v>12:30</x:v>
       </x:c>
-      <x:c r="C28" s="14" t="str">
+      <x:c r="C28" s="17" t="str">
         <x:v>Cash</x:v>
       </x:c>
-      <x:c r="D28" s="15"/>
+      <x:c r="D28" s="18"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="16" t="str">
+      <x:c r="A29" s="19" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B29" s="17" t="str">
+      <x:c r="B29" s="20" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="C29" s="17" t="str">
+      <x:c r="C29" s="20" t="str">
         <x:v>Price (RM)</x:v>
       </x:c>
-      <x:c r="D29" s="18" t="str">
+      <x:c r="D29" s="21" t="str">
         <x:v>Amount (RM)</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="19" t="str">
+      <x:c r="A30" s="22" t="str">
         <x:v>Ikan Tilapia (11 ekor)</x:v>
       </x:c>
-      <x:c r="B30" s="20" t="str">
+      <x:c r="B30" s="23" t="str">
         <x:v>8 kg</x:v>
       </x:c>
-      <x:c r="C30" s="21">
+      <x:c r="C30" s="24">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D30" s="22">
+      <x:c r="D30" s="25">
         <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="23" t="str">
+      <x:c r="A31" s="26" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B31" s="24"/>
-      <x:c r="C31" s="24"/>
-      <x:c r="D31" s="25">
+      <x:c r="B31" s="27"/>
+      <x:c r="C31" s="27"/>
+      <x:c r="D31" s="28">
         <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="13" t="str">
+      <x:c r="A33" s="16" t="str">
         <x:v>Inv #1006 — Kak Ros</x:v>
       </x:c>
-      <x:c r="B33" s="14" t="str">
+      <x:c r="B33" s="17" t="str">
         <x:v>13:20</x:v>
       </x:c>
-      <x:c r="C33" s="14" t="str">
+      <x:c r="C33" s="17" t="str">
         <x:v>Credit</x:v>
       </x:c>
-      <x:c r="D33" s="15"/>
+      <x:c r="D33" s="18"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="16" t="str">
+      <x:c r="A34" s="19" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B34" s="17" t="str">
+      <x:c r="B34" s="20" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="C34" s="17" t="str">
+      <x:c r="C34" s="20" t="str">
         <x:v>Price (RM)</x:v>
       </x:c>
-      <x:c r="D34" s="18" t="str">
+      <x:c r="D34" s="21" t="str">
         <x:v>Amount (RM)</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="19" t="str">
+      <x:c r="A35" s="22" t="str">
         <x:v>Ikan Tilapia (3 ekor)</x:v>
       </x:c>
-      <x:c r="B35" s="20" t="str">
+      <x:c r="B35" s="23" t="str">
         <x:v>2.4 kg</x:v>
       </x:c>
-      <x:c r="C35" s="21">
+      <x:c r="C35" s="24">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D35" s="22">
+      <x:c r="D35" s="25">
         <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="19" t="str">
+      <x:c r="A36" s="22" t="str">
         <x:v>Sayur Campur</x:v>
       </x:c>
-      <x:c r="B36" s="20" t="str">
+      <x:c r="B36" s="23" t="str">
         <x:v>1.5 kg</x:v>
       </x:c>
-      <x:c r="C36" s="21">
+      <x:c r="C36" s="24">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D36" s="22">
+      <x:c r="D36" s="25">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="26" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="24"/>
-      <x:c r="C37" s="24"/>
-      <x:c r="D37" s="25">
+      <x:c r="B37" s="27"/>
+      <x:c r="C37" s="27"/>
+      <x:c r="D37" s="28">
         <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="26" t="str">
+      <x:c r="A39" s="29" t="str">
         <x:v>Inv #1007</x:v>
       </x:c>
-      <x:c r="B39" s="27" t="str">
+      <x:c r="B39" s="30" t="str">
         <x:v>14:10</x:v>
       </x:c>
-      <x:c r="C39" s="27" t="str">
+      <x:c r="C39" s="30" t="str">
         <x:v>Cash</x:v>
       </x:c>
-      <x:c r="D39" s="28" t="str">
+      <x:c r="D39" s="31" t="str">
         <x:v>VOIDED</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="16" t="str">
+      <x:c r="A40" s="19" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B40" s="17" t="str">
+      <x:c r="B40" s="20" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="C40" s="17" t="str">
+      <x:c r="C40" s="20" t="str">
         <x:v>Price (RM)</x:v>
       </x:c>
-      <x:c r="D40" s="18" t="str">
+      <x:c r="D40" s="21" t="str">
         <x:v>Amount (RM)</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="29" t="str">
+      <x:c r="A41" s="32" t="str">
         <x:v>Ikan Tilapia (2 ekor)</x:v>
       </x:c>
-      <x:c r="B41" s="30" t="str">
+      <x:c r="B41" s="33" t="str">
         <x:v>1 kg</x:v>
       </x:c>
-      <x:c r="C41" s="31">
+      <x:c r="C41" s="34">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D41" s="32">
+      <x:c r="D41" s="35">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="33" t="str">
+      <x:c r="A42" s="36" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B42" s="24"/>
-      <x:c r="C42" s="24"/>
-      <x:c r="D42" s="34">
+      <x:c r="B42" s="27"/>
+      <x:c r="C42" s="27"/>
+      <x:c r="D42" s="37">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="13" t="str">
+      <x:c r="A44" s="16" t="str">
         <x:v>Inv #1008</x:v>
       </x:c>
-      <x:c r="B44" s="14" t="str">
+      <x:c r="B44" s="17" t="str">
         <x:v>16:45</x:v>
       </x:c>
-      <x:c r="C44" s="14" t="str">
+      <x:c r="C44" s="17" t="str">
         <x:v>QR</x:v>
       </x:c>
-      <x:c r="D44" s="15"/>
+      <x:c r="D44" s="18"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="16" t="str">
+      <x:c r="A45" s="19" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B45" s="17" t="str">
+      <x:c r="B45" s="20" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="C45" s="17" t="str">
+      <x:c r="C45" s="20" t="str">
         <x:v>Price (RM)</x:v>
       </x:c>
-      <x:c r="D45" s="18" t="str">
+      <x:c r="D45" s="21" t="str">
         <x:v>Amount (RM)</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="19" t="str">
+      <x:c r="A46" s="22" t="str">
         <x:v>Fresh Milk 1 L</x:v>
       </x:c>
-      <x:c r="B46" s="20" t="str">
+      <x:c r="B46" s="23" t="str">
         <x:v>4 bottle</x:v>
       </x:c>
-      <x:c r="C46" s="21">
+      <x:c r="C46" s="24">
         <x:v>6.8</x:v>
       </x:c>
-      <x:c r="D46" s="22">
+      <x:c r="D46" s="25">
         <x:v>27.2</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="19" t="str">
+      <x:c r="A47" s="22" t="str">
         <x:v>Ais Tube</x:v>
       </x:c>
-      <x:c r="B47" s="20" t="str">
+      <x:c r="B47" s="23" t="str">
         <x:v>2 bag</x:v>
       </x:c>
-      <x:c r="C47" s="21">
+      <x:c r="C47" s="24">
         <x:v>3.5</x:v>
       </x:c>
-      <x:c r="D47" s="22">
+      <x:c r="D47" s="25">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="23" t="str">
+      <x:c r="A48" s="26" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B48" s="24"/>
-      <x:c r="C48" s="24"/>
-      <x:c r="D48" s="25">
+      <x:c r="B48" s="27"/>
+      <x:c r="C48" s="27"/>
+      <x:c r="D48" s="28">
         <x:v>34.2</x:v>
       </x:c>
     </x:row>
@@ -1417,7 +1486,7 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="35" t="str">
+      <x:c r="A4" s="38" t="str">
         <x:v>ADDED TODAY — 2026-08-10</x:v>
       </x:c>
     </x:row>
@@ -1475,7 +1544,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="36" t="str">
+      <x:c r="A10" s="39" t="str">
         <x:v>ALL OUTSTANDING</x:v>
       </x:c>
     </x:row>
@@ -1575,7 +1644,7 @@
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="12" t="str">
+      <x:c r="A19" s="10" t="str">
         <x:v>BY CREDITOR</x:v>
       </x:c>
     </x:row>
@@ -1594,7 +1663,7 @@
       <x:c r="A21" t="str">
         <x:v>Pak Abu</x:v>
       </x:c>
-      <x:c r="C21" s="11">
+      <x:c r="C21" s="15">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D21" s="6">
@@ -1605,7 +1674,7 @@
       <x:c r="A22" t="str">
         <x:v>Restoran Selera</x:v>
       </x:c>
-      <x:c r="C22" s="11">
+      <x:c r="C22" s="15">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D22" s="6">
@@ -1616,7 +1685,7 @@
       <x:c r="A23" t="str">
         <x:v>Kak Ros</x:v>
       </x:c>
-      <x:c r="C23" s="11">
+      <x:c r="C23" s="15">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D23" s="6">
@@ -1635,12 +1704,16 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="5">
+  <x:mergeCells count="9">
     <x:mergeCell ref="A1:D1"/>
     <x:mergeCell ref="A2:D2"/>
     <x:mergeCell ref="A4:D4"/>
     <x:mergeCell ref="A10:D10"/>
     <x:mergeCell ref="A19:D19"/>
+    <x:mergeCell ref="A20:B20"/>
+    <x:mergeCell ref="A21:B21"/>
+    <x:mergeCell ref="A22:B22"/>
+    <x:mergeCell ref="A23:B23"/>
   </x:mergeCells>
 </x:worksheet>
 </file>